--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-observation-labresult.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common</t>
+    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -383,7 +383,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -618,7 +618,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -697,7 +697,7 @@
     <t>Observation.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -726,7 +726,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -758,7 +758,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|1.3.0-dev|MedicationStatement|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|1.3.0-dev|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -832,7 +832,7 @@
     <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -913,7 +913,7 @@
 (social-history | vital-signs | imaging | laboratory | procedure | survey | exam | therapy | activity)</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS|1.1.0</t>
   </si>
   <si>
     <t>Observation.category:first.id</t>
@@ -1101,7 +1101,7 @@
     <t>MEDIS 臨床検査マスター</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationLabResultCode_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationLabResultCode_VS|1.1.0</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1201,7 +1201,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1232,7 +1232,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1252,7 +1252,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1346,7 +1346,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|CareTeam|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev|CareTeam|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1497,7 +1497,7 @@
     <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1531,7 +1531,7 @@
     <t>観測の解釈を識別するコード。 / Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1581,7 +1581,7 @@
     <t>Observation.note.author[x]</t>
   </si>
   <si>
-    <t>Reference(Practitioner|Patient|RelatedPerson|Organization)
+    <t>Reference(Practitioner|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 string</t>
   </si>
   <si>
@@ -1653,7 +1653,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS|1.3.0-dev</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1688,7 +1688,7 @@
     <t>単純な観測の方法。 / Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1700,7 +1700,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1728,7 +1728,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1809,7 +1809,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1862,7 +1862,7 @@
     <t>参照範囲の意味のコード。 / Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1895,7 +1895,7 @@
     <t>参照範囲が適用される母集団を識別するコード。 / Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1935,7 +1935,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|QuestionnaireResponse|MolecularSequence)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -1957,7 +1957,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|MolecularSequence)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -2018,7 +2018,7 @@
     <t>単純な観測の名前を識別するコード。 / Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -2417,7 +2417,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="132.98828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="54.09375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="58.62109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-observation-labresult.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev</t>
+    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -383,7 +383,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -618,7 +618,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -697,7 +697,7 @@
     <t>Observation.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(Organization)
 </t>
   </si>
   <si>
@@ -726,7 +726,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(ServiceRequest)
 </t>
   </si>
   <si>
@@ -758,7 +758,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|1.3.0-dev|MedicationStatement|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|1.3.0-dev|ImagingStudy|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
 </t>
   </si>
   <si>
@@ -832,7 +832,7 @@
     <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -913,7 +913,7 @@
 (social-history | vital-signs | imaging | laboratory | procedure | survey | exam | therapy | activity)</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
     <t>Observation.category:first.id</t>
@@ -1101,7 +1101,7 @@
     <t>MEDIS 臨床検査マスター</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationLabResultCode_VS|1.1.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationLabResultCode_VS</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1201,7 +1201,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient)
 </t>
   </si>
   <si>
@@ -1232,7 +1232,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
@@ -1252,7 +1252,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Encounter)
 </t>
   </si>
   <si>
@@ -1346,7 +1346,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|1.3.0-dev|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|1.3.0-dev|CareTeam|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|1.3.0-dev|RelatedPerson|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization|CareTeam|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -1497,7 +1497,7 @@
     <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1531,7 +1531,7 @@
     <t>観測の解釈を識別するコード。 / Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1581,7 +1581,7 @@
     <t>Observation.note.author[x]</t>
   </si>
   <si>
-    <t>Reference(Practitioner|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
+    <t>Reference(Practitioner|Patient|RelatedPerson|Organization)
 string</t>
   </si>
   <si>
@@ -1653,7 +1653,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS|1.3.0-dev</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1688,7 +1688,7 @@
     <t>単純な観測の方法。 / Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1700,7 +1700,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common)
 </t>
   </si>
   <si>
@@ -1728,7 +1728,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
+    <t xml:space="preserve">Reference(Device|DeviceMetric)
 </t>
   </si>
   <si>
@@ -1809,7 +1809,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
+    <t xml:space="preserve">Quantity {SimpleQuantity}
 </t>
   </si>
   <si>
@@ -1862,7 +1862,7 @@
     <t>参照範囲の意味のコード。 / Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1895,7 +1895,7 @@
     <t>参照範囲が適用される母集団を識別するコード。 / Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1935,7 +1935,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|QuestionnaireResponse|MolecularSequence)
 </t>
   </si>
   <si>
@@ -1957,7 +1957,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|1.3.0-dev|MolecularSequence|4.0.1)
+    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|MolecularSequence)
 </t>
   </si>
   <si>
@@ -2018,7 +2018,7 @@
     <t>単純な観測の名前を識別するコード。 / Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -2417,7 +2417,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="132.98828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="58.62109375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.09375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
